--- a/optimized_version/metadata/testing_daily_metrics/agus7_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus7_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3052262016736704</v>
+        <v>0.2712751905432328</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07741055358987126</v>
+        <v>0.06880000000000308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07741055358987126</v>
+        <v>0.06880000000000308</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>2.852841481614374</v>
+        <v>2.850860719727955</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6581758794658232</v>
+        <v>0.6574583333333339</v>
       </c>
       <c r="F3" t="n">
-        <v>1.023595148476596</v>
+        <v>1.02405380962135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5100622230196251</v>
+        <v>0.5096230537481157</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>1.336127802280104</v>
+        <v>1.336496406631338</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3233625000000011</v>
+        <v>0.3233625000000015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5388956571125768</v>
+        <v>0.5383991560636034</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6373174476949495</v>
+        <v>0.6379854408852625</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>6.970652627895952</v>
+        <v>6.965820187849596</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.332280925598312</v>
+        <v>1.330845833333334</v>
       </c>
       <c r="F5" t="n">
-        <v>2.534277501061945</v>
+        <v>2.534495814341911</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08019954036077448</v>
+        <v>0.0800410626058714</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>2.81941848834637</v>
+        <v>2.814885103574372</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6822684255983118</v>
+        <v>0.6810750000000003</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9845264433340924</v>
+        <v>0.98388139560874</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5549305102070023</v>
+        <v>-0.5528936409723104</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9154183888877223</v>
+        <v>0.915554682280776</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2296958333333325</v>
+        <v>0.2296958333333336</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2878092918842972</v>
+        <v>0.2883547374040065</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0597577851001736</v>
+        <v>0.05619058358124396</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>1.295427731720471</v>
+        <v>1.29553204188949</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3199791666666664</v>
+        <v>0.3199791666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4754137329083856</v>
+        <v>0.4759929345589073</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1666396721601067</v>
+        <v>-0.1694840630352961</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>6.451580665693989</v>
+        <v>6.466186992513562</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.327663148803377</v>
+        <v>1.330533333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>2.054859051375358</v>
+        <v>2.055134106532548</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3393977732087373</v>
+        <v>0.3392209102651103</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>10.98973924079456</v>
+        <v>10.98185762522007</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.754402638397467</v>
+        <v>1.752249999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.950722241394798</v>
+        <v>2.950666465111455</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6372571546032946</v>
+        <v>0.637270868029939</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>6.813994023900118</v>
+        <v>6.812647495651119</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.497592546132489</v>
+        <v>1.496875</v>
       </c>
       <c r="F11" t="n">
-        <v>2.292405647569558</v>
+        <v>2.292774918630261</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3762031837627904</v>
+        <v>-0.3766465895281557</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>3.516613397298435</v>
+        <v>3.517355613421162</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8208291666666664</v>
+        <v>0.8208291666666665</v>
       </c>
       <c r="F12" t="n">
-        <v>1.13544920629771</v>
+        <v>1.134433580581075</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3567445144960855</v>
+        <v>0.3578947458371534</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>3.184379012456859</v>
+        <v>3.179066843658065</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.722380925598312</v>
+        <v>0.7209458333333337</v>
       </c>
       <c r="F13" t="n">
-        <v>1.029128608270059</v>
+        <v>1.030215017403325</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5815882792830689</v>
+        <v>0.5807044125928136</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>3.462457680983944</v>
+        <v>3.45634223130967</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7340434255983116</v>
+        <v>0.7326083333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>0.93309660899028</v>
+        <v>0.9331701501691246</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2958257016947656</v>
+        <v>-0.296029968442963</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>5.30520803061329</v>
+        <v>5.306304315652661</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.166283333333333</v>
+        <v>1.166283333333332</v>
       </c>
       <c r="F15" t="n">
-        <v>1.626317154102605</v>
+        <v>1.62616079821974</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9214287432157313</v>
+        <v>-0.9210593045179001</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>3.387590044556646</v>
+        <v>3.394552454981429</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7843649077350215</v>
+        <v>0.7858000000000004</v>
       </c>
       <c r="F16" t="n">
-        <v>1.396648578835014</v>
+        <v>1.396867469181788</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1546110814539206</v>
+        <v>-0.1549730236471114</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>7.280507740414619</v>
+        <v>7.278607030769709</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2.043339258931645</v>
+        <v>2.041904166666667</v>
       </c>
       <c r="F17" t="n">
-        <v>3.917123259938016</v>
+        <v>3.915861975191414</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6022250041113713</v>
+        <v>0.6024811240895016</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>1.511610247269256</v>
+        <v>1.511692566210809</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -893,10 +893,10 @@
         <v>0.5380999999999986</v>
       </c>
       <c r="F18" t="n">
-        <v>0.746080745984733</v>
+        <v>0.7461606987327399</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0373730273200118</v>
+        <v>0.03716669899403946</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>5.724768691285786</v>
+        <v>5.72198017077879</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.561380046132489</v>
+        <v>1.5606625</v>
       </c>
       <c r="F19" t="n">
-        <v>2.738422531281014</v>
+        <v>2.739330805522278</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6899811971470926</v>
+        <v>0.6897755102693368</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>4.71018071144908</v>
+        <v>4.70422784901848</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5294484717308</v>
+        <v>1.527295833333333</v>
       </c>
       <c r="F20" t="n">
-        <v>1.994143788666259</v>
+        <v>1.992790016220976</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6095479421851138</v>
+        <v>0.6100778977674131</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>4.190045339994888</v>
+        <v>4.190443868565334</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -971,10 +971,10 @@
         <v>1.360823611111112</v>
       </c>
       <c r="F21" t="n">
-        <v>2.312427944996109</v>
+        <v>2.312003256467574</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1248867548122092</v>
+        <v>0.125208162819319</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>3.758372938841579</v>
+        <v>3.758926452642829</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -997,10 +997,10 @@
         <v>1.378229166666666</v>
       </c>
       <c r="F22" t="n">
-        <v>1.66130816988517</v>
+        <v>1.661132796843767</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.03336368583756566</v>
+        <v>-0.03314552695477091</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>5.193181759445615</v>
+        <v>5.193703743434939</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1023,10 +1023,10 @@
         <v>1.732583333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>2.275664948725101</v>
+        <v>2.276139393432074</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6442754344378114</v>
+        <v>0.6441270916594571</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>2.864375438768134</v>
+        <v>2.859052850448966</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.10970263839868</v>
+        <v>1.107550000004851</v>
       </c>
       <c r="F24" t="n">
-        <v>1.436716413418992</v>
+        <v>1.436311932531855</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2551512824900516</v>
+        <v>0.2555706201655159</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>4.153298997057424</v>
+        <v>4.155679699954291</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.557190787200845</v>
+        <v>1.557908333333334</v>
       </c>
       <c r="F25" t="n">
-        <v>1.936208496543725</v>
+        <v>1.936306010810276</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.04212910519051238</v>
+        <v>-0.04223407840445814</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>4.103738739908436</v>
+        <v>4.1060103096646</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.540107453867512</v>
+        <v>1.540824999995151</v>
       </c>
       <c r="F26" t="n">
-        <v>2.03920681675901</v>
+        <v>2.039262178868735</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4175475134535738</v>
+        <v>-0.4176244840537449</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>3.149768656330608</v>
+        <v>3.144570919947257</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.213731805064741</v>
+        <v>1.211579166729726</v>
       </c>
       <c r="F27" t="n">
-        <v>1.548670465869557</v>
+        <v>1.548326491372019</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1400324761366163</v>
+        <v>-0.1395261081809471</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>3.773407504811368</v>
+        <v>3.770145562904156</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.535401758940436</v>
+        <v>1.533966667117775</v>
       </c>
       <c r="F28" t="n">
-        <v>2.136212360561498</v>
+        <v>2.13594763654902</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2660149656902823</v>
+        <v>0.2661968684146726</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>3.814861421584225</v>
+        <v>3.817157328613718</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.477844953867511</v>
+        <v>1.478562499995149</v>
       </c>
       <c r="F29" t="n">
-        <v>1.990709302592596</v>
+        <v>1.991540352226951</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.04474863991950051</v>
+        <v>-0.04562111206111563</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>6.008064690911016</v>
+        <v>6.010554744639497</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2.285657453868116</v>
+        <v>2.286375000033953</v>
       </c>
       <c r="F30" t="n">
-        <v>2.979396954397631</v>
+        <v>2.979142003352116</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4953274808632895</v>
+        <v>-0.4950715774042633</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>4.911400286037218</v>
+        <v>4.911836446598086</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1231,10 +1231,10 @@
         <v>1.971641666666666</v>
       </c>
       <c r="F31" t="n">
-        <v>2.555915607013776</v>
+        <v>2.555327344490328</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3056540330581755</v>
+        <v>0.3059736138023794</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>3.906567036356553</v>
+        <v>3.905248565562907</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.65991754613249</v>
+        <v>1.659200000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>2.473308946511238</v>
+        <v>2.473220296159105</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5511447615426492</v>
+        <v>-0.5510335687495689</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>4.922416173381006</v>
+        <v>4.92305160127466</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1283,10 +1283,10 @@
         <v>1.975750000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>2.415486295670975</v>
+        <v>2.416181506875398</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.08344354722390412</v>
+        <v>-0.08406729780260935</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>7.432478551316378</v>
+        <v>7.432679374280085</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.487280046132489</v>
+        <v>2.4865625</v>
       </c>
       <c r="F34" t="n">
-        <v>4.181024590261878</v>
+        <v>4.180790509331539</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6316448545351829</v>
+        <v>0.6316860992107733</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>5.503924692081414</v>
+        <v>5.506464765861352</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.19843245386751</v>
+        <v>2.199149999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>2.808091244563156</v>
+        <v>2.808382694126045</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.825748478321412</v>
+        <v>-0.8261274839614932</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>2.668203611302356</v>
+        <v>2.671849226459196</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.096373241068356</v>
+        <v>1.097808333333334</v>
       </c>
       <c r="F36" t="n">
-        <v>1.285670973511787</v>
+        <v>1.285101651297153</v>
       </c>
       <c r="G36" t="n">
-        <v>0.470060022716686</v>
+        <v>0.4705292559912675</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.2535206697844565</v>
+        <v>0.2744925683640412</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1040894464101291</v>
+        <v>0.1126999999999973</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1040894464101291</v>
+        <v>0.1126999999999973</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9790945211204648</v>
+        <v>0.9754927514792912</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>5.52230236592062</v>
+        <v>5.526487596017698</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2.201244074401689</v>
+        <v>2.202679166666667</v>
       </c>
       <c r="F38" t="n">
-        <v>3.214695634442413</v>
+        <v>3.214237799035722</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1975913142443761</v>
+        <v>-0.1972502177771136</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>4.332847688713334</v>
+        <v>4.333262078548036</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1439,10 +1439,10 @@
         <v>1.718845833333333</v>
       </c>
       <c r="F39" t="n">
-        <v>2.138665778982285</v>
+        <v>2.139678308667761</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1181178888195226</v>
+        <v>0.1172826548150261</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>3.550995264115194</v>
+        <v>3.551253442284056</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1465,10 +1465,10 @@
         <v>1.381954166666667</v>
       </c>
       <c r="F40" t="n">
-        <v>1.864788073012823</v>
+        <v>1.864650924771176</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2033529441330548</v>
+        <v>-0.2031759463564171</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>5.539440749323282</v>
+        <v>5.545566604299404</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2.193805694935866</v>
+        <v>2.195958333333333</v>
       </c>
       <c r="F41" t="n">
-        <v>2.9329513075802</v>
+        <v>2.93312780165361</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2954844499259208</v>
+        <v>-0.2956403694643917</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>4.831591648683025</v>
+        <v>4.831854660208456</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1517,10 +1517,10 @@
         <v>2.0272875</v>
       </c>
       <c r="F42" t="n">
-        <v>2.668045509815041</v>
+        <v>2.667310147804964</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2837402046810175</v>
+        <v>0.2841349787996824</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>5.613992315390274</v>
+        <v>5.616474292616772</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2.252136620534177</v>
+        <v>2.252854166666665</v>
       </c>
       <c r="F43" t="n">
-        <v>3.005839647546634</v>
+        <v>3.006316802514886</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.3656017084002419</v>
+        <v>-0.3660353012959865</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>4.45237699235553</v>
+        <v>4.454635431536754</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.740011620534177</v>
+        <v>1.740729166666666</v>
       </c>
       <c r="F44" t="n">
-        <v>2.191852874145258</v>
+        <v>2.191985810572231</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.4024536354486776</v>
+        <v>-0.4026237589375496</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>3.33732232267686</v>
+        <v>3.330615641154604</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.332436851196624</v>
+        <v>1.329566666666668</v>
       </c>
       <c r="F45" t="n">
-        <v>1.607511136324404</v>
+        <v>1.606271147201908</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1375442009988596</v>
+        <v>0.1388742363793988</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>4.070948969805951</v>
+        <v>4.07650509154271</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.604909861602531</v>
+        <v>1.607062499999999</v>
       </c>
       <c r="F46" t="n">
-        <v>2.225873553797646</v>
+        <v>2.226263803906296</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.08415892181622531</v>
+        <v>-0.08453911432590488</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>7.539538253191987</v>
+        <v>7.544523314314551</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2.58531907440169</v>
+        <v>2.586754166666668</v>
       </c>
       <c r="F47" t="n">
-        <v>3.873939845480332</v>
+        <v>3.87416762463242</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6935910597552661</v>
+        <v>0.6935550263509082</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>3.676123219290639</v>
+        <v>3.678346324270652</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.462490787200845</v>
+        <v>1.463208333333333</v>
       </c>
       <c r="F48" t="n">
-        <v>1.815128512607963</v>
+        <v>1.814818930132333</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.3211097784794672</v>
+        <v>-0.3206591684485598</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>5.046908407115903</v>
+        <v>5.045566586300291</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.963288379465824</v>
+        <v>1.962570833333335</v>
       </c>
       <c r="F49" t="n">
-        <v>2.497904740984761</v>
+        <v>2.498058846968315</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.4200156293637241</v>
+        <v>-0.4201908479395042</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>4.231489770042108</v>
+        <v>4.228520374548744</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.76583092559831</v>
+        <v>1.764395833333332</v>
       </c>
       <c r="F50" t="n">
-        <v>2.397595365023409</v>
+        <v>2.397845065105332</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.2279447427187964</v>
+        <v>-0.22820052722176</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>3.972404024944358</v>
+        <v>3.971090463221413</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.572650879465823</v>
+        <v>1.571933333333334</v>
       </c>
       <c r="F51" t="n">
-        <v>2.157670973416323</v>
+        <v>2.157166339591518</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.3337549841738339</v>
+        <v>-0.3331311826950425</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>4.498237084828697</v>
+        <v>4.493358040118413</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.788652638397467</v>
+        <v>1.7865</v>
       </c>
       <c r="F52" t="n">
-        <v>2.31083014352016</v>
+        <v>2.311071877758601</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.7766876172446802</v>
+        <v>-0.7770593526519098</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>2.390531906377969</v>
+        <v>2.390395020570546</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9339467127991549</v>
+        <v>0.9338124999999996</v>
       </c>
       <c r="F53" t="n">
-        <v>1.595852404643051</v>
+        <v>1.596132404830501</v>
       </c>
       <c r="G53" t="n">
-        <v>0.009453207828489019</v>
+        <v>0.009105584679654943</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>3.410210344430976</v>
+        <v>3.406983616014978</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1.343980925598311</v>
+        <v>1.342545833333333</v>
       </c>
       <c r="F54" t="n">
-        <v>1.757403254334079</v>
+        <v>1.756785179549091</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.08748587039219702</v>
+        <v>-0.08672107221913983</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>4.315858218363497</v>
+        <v>4.319621136134319</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.747502407735022</v>
+        <v>1.7489375</v>
       </c>
       <c r="F55" t="n">
-        <v>2.587591752716495</v>
+        <v>2.587793534316447</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.468765793525626</v>
+        <v>-0.4689948725269739</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>1.820515930598024</v>
+        <v>1.815391424715606</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7413443050641361</v>
+        <v>0.739191666666669</v>
       </c>
       <c r="F56" t="n">
-        <v>1.163649866348486</v>
+        <v>1.163243764579608</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.03244543185175464</v>
+        <v>-0.03172493204087412</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>5.704904540351563</v>
+        <v>5.70739775741431</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2.274219953867511</v>
+        <v>2.2749375</v>
       </c>
       <c r="F57" t="n">
-        <v>3.122627881125083</v>
+        <v>3.123148077461266</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.2297877795805023</v>
+        <v>-0.2301975526356006</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>4.654150095329463</v>
+        <v>4.651185284759365</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.772839258931646</v>
+        <v>1.771404166666668</v>
       </c>
       <c r="F58" t="n">
-        <v>2.402462992484349</v>
+        <v>2.401906096598076</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1355491026738465</v>
+        <v>0.1359498192337223</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>5.212930465764561</v>
+        <v>5.213371310095813</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1959,10 +1959,10 @@
         <v>2.102658333333333</v>
       </c>
       <c r="F59" t="n">
-        <v>2.917974416927792</v>
+        <v>2.91759954343178</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.2119619391747682</v>
+        <v>-0.2116505565784088</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>4.014994500884812</v>
+        <v>4.01544060921674</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1985,10 +1985,10 @@
         <v>1.587583333333334</v>
       </c>
       <c r="F60" t="n">
-        <v>2.137375779610359</v>
+        <v>2.138688666761325</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6841780720471337</v>
+        <v>0.6837899644420791</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>4.748523308574262</v>
+        <v>4.745272356930686</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.980635092264979</v>
+        <v>1.979200000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>2.494871065329404</v>
+        <v>2.494111127235514</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1481306521077124</v>
+        <v>0.1486495321278354</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>4.219547527004134</v>
+        <v>4.219817097123104</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2037,10 +2037,10 @@
         <v>1.620525000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>2.168361821257564</v>
+        <v>2.169003649720304</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.07576626001869391</v>
+        <v>-0.07640320131216694</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>4.46770433248615</v>
+        <v>4.47178989519956</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.803594074401689</v>
+        <v>1.805029166666667</v>
       </c>
       <c r="F63" t="n">
-        <v>2.796139117188094</v>
+        <v>2.796165160611345</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.3308246248485449</v>
+        <v>-0.3308494157397954</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>5.9465235478356</v>
+        <v>5.942118197607523</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2.324090138397467</v>
+        <v>2.3219375</v>
       </c>
       <c r="F64" t="n">
-        <v>3.455896314181454</v>
+        <v>3.45515435068874</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.2061200651495172</v>
+        <v>-0.2056022249657368</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>6.139733824552832</v>
+        <v>6.143586928665279</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2.366048241068356</v>
+        <v>2.367483333333334</v>
       </c>
       <c r="F65" t="n">
-        <v>3.223959063261976</v>
+        <v>3.224898767145</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1510743216846329</v>
+        <v>-0.1517454385495276</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>4.889346169278802</v>
+        <v>4.884518812440886</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.854902638397467</v>
+        <v>1.85275</v>
       </c>
       <c r="F66" t="n">
-        <v>2.670168218431758</v>
+        <v>2.669787549444087</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.494696838764543</v>
+        <v>-0.4942706902018541</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>3.870364982367997</v>
+        <v>3.867272557009777</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.526114258931645</v>
+        <v>1.524679166666667</v>
       </c>
       <c r="F67" t="n">
-        <v>2.035578153603295</v>
+        <v>2.036005618903919</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.8907951894544468</v>
+        <v>-0.891589395461829</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>2.211948836737732</v>
+        <v>2.203448373818924</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9364844434616018</v>
+        <v>0.9326958333333337</v>
       </c>
       <c r="F68" t="n">
-        <v>1.327174047892741</v>
+        <v>1.324933504463525</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7461442131634157</v>
+        <v>0.7470006114804325</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>6.892777869635023</v>
+        <v>6.895205501138914</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2.818632453867512</v>
+        <v>2.81935</v>
       </c>
       <c r="F69" t="n">
-        <v>3.232610120687892</v>
+        <v>3.233294881644214</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.2896340970254765</v>
+        <v>-0.2901805190045055</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>2.907407376766001</v>
+        <v>2.904253364111011</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.155285092264977</v>
+        <v>1.153849999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1.620493223397034</v>
+        <v>1.620380234440874</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.4609417502002979</v>
+        <v>-0.4607380288564302</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>3.859309850062699</v>
+        <v>3.857987592398426</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.523134212799156</v>
+        <v>1.522416666666667</v>
       </c>
       <c r="F71" t="n">
-        <v>2.146413606114826</v>
+        <v>2.146474058970509</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.5677027950687095</v>
+        <v>-0.5677911037200929</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>2.80413088022022</v>
+        <v>2.809703442845686</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1.129343194935866</v>
+        <v>1.131495833333333</v>
       </c>
       <c r="F72" t="n">
-        <v>1.779976586956992</v>
+        <v>1.780041765076503</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.332995662596677</v>
+        <v>-0.3330932860619964</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>3.523326879241166</v>
+        <v>3.522163523956185</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.408538379465823</v>
+        <v>1.407820833333334</v>
       </c>
       <c r="F73" t="n">
-        <v>1.983456108618688</v>
+        <v>1.983451075251584</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.1035033537977526</v>
+        <v>-0.1034977531389756</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>2.20198557007074</v>
+        <v>2.198786342316326</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9245350922649793</v>
+        <v>0.9231000000000013</v>
       </c>
       <c r="F74" t="n">
-        <v>1.259896441093947</v>
+        <v>1.258900704649365</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5931950141776192</v>
+        <v>0.5938377820542635</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>6.843772393199508</v>
+        <v>6.849477168929775</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2.3032765282692</v>
+        <v>2.305429166666667</v>
       </c>
       <c r="F75" t="n">
-        <v>3.830867508605695</v>
+        <v>3.831305815553187</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5664982339275231</v>
+        <v>0.5663990304415425</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>2.641486983897435</v>
+        <v>2.638228024859346</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1.037889258931644</v>
+        <v>1.036454166666666</v>
       </c>
       <c r="F76" t="n">
-        <v>1.599629835351112</v>
+        <v>1.599439669201894</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.164498180334856</v>
+        <v>-1.163983574007545</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>3.628969802427752</v>
+        <v>3.626090782684265</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.561405925598311</v>
+        <v>1.559970833333334</v>
       </c>
       <c r="F77" t="n">
-        <v>2.096911848495545</v>
+        <v>2.096324560490733</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.7268431010835938</v>
+        <v>-0.7258759529207655</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>1.630822609549108</v>
+        <v>1.629350556924891</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7439508794658215</v>
+        <v>0.7432333333333325</v>
       </c>
       <c r="F78" t="n">
-        <v>1.028330495770791</v>
+        <v>1.027625663848466</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1344511080011666</v>
+        <v>-0.1328965040465264</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>2.116007351313697</v>
+        <v>2.116095413294667</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2479,10 +2479,10 @@
         <v>0.8679833333333337</v>
       </c>
       <c r="F79" t="n">
-        <v>1.361834100636115</v>
+        <v>1.363806920901928</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7805879038770724</v>
+        <v>0.7799517409828443</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>4.075911099189885</v>
+        <v>4.074532118398058</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1.611555046132489</v>
+        <v>1.6108375</v>
       </c>
       <c r="F80" t="n">
-        <v>2.194558246929852</v>
+        <v>2.194284881895846</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5784778188844975</v>
+        <v>-0.5780845973618394</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>4.43600049759369</v>
+        <v>4.438214894978524</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.799865787200844</v>
+        <v>1.800583333333333</v>
       </c>
       <c r="F81" t="n">
-        <v>2.161325840252094</v>
+        <v>2.161521636727624</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.4481652955450719</v>
+        <v>-0.4484276886548026</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>2.521637547962954</v>
+        <v>2.527165841438336</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1.023389028269199</v>
+        <v>1.025541666666666</v>
       </c>
       <c r="F82" t="n">
-        <v>1.346922008512059</v>
+        <v>1.347137660003608</v>
       </c>
       <c r="G82" t="n">
-        <v>-1.45350750026392</v>
+        <v>-1.454293210060177</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>4.712178000567699</v>
+        <v>4.70997328997899</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.96904485481607</v>
+        <v>1.967921739130435</v>
       </c>
       <c r="F83" t="n">
-        <v>2.80979242647842</v>
+        <v>2.809087424769831</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.3867877365607555</v>
+        <v>-0.386091909310831</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/testing_daily_metrics/agus7_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus7_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2712751905432328</v>
+        <v>0.05914430026378582</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06880000000000308</v>
+        <v>0.01500000000000057</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06880000000000308</v>
+        <v>0.01500000000000057</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>2.850860719727955</v>
+        <v>2.784501546296173</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6574583333333339</v>
+        <v>0.6427639993306123</v>
       </c>
       <c r="F3" t="n">
-        <v>1.02405380962135</v>
+        <v>0.9948521703478593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5096230537481157</v>
+        <v>0.5371912159888708</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>1.336496406631338</v>
+        <v>1.221593754242135</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3233625000000015</v>
+        <v>0.2962818340027218</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5383991560636034</v>
+        <v>0.5209151579431013</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6379854408852625</v>
+        <v>0.6611158272834838</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>6.965820187849596</v>
+        <v>7.050690846733637</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.330845833333334</v>
+        <v>1.352909832799763</v>
       </c>
       <c r="F5" t="n">
-        <v>2.534495814341911</v>
+        <v>2.555496979170703</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0800410626058714</v>
+        <v>0.06473209735562191</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>2.814885103574372</v>
+        <v>2.893846519099053</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6810750000000003</v>
+        <v>0.700761000669388</v>
       </c>
       <c r="F6" t="n">
-        <v>0.98388139560874</v>
+        <v>0.9781685103398073</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5528936409723104</v>
+        <v>-0.5349123128306057</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.915554682280776</v>
+        <v>0.8704062621083518</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2296958333333336</v>
+        <v>0.2183818326639462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2883547374040065</v>
+        <v>0.3006140034389563</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05619058358124396</v>
+        <v>-0.02576656484947737</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>1.29553204188949</v>
+        <v>1.390959495942348</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3199791666666667</v>
+        <v>0.3442985005335708</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4759929345589073</v>
+        <v>0.4742564469491934</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1694840630352961</v>
+        <v>-0.1609667505743693</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>6.466186992513562</v>
+        <v>6.470213359919401</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.330533333333333</v>
+        <v>1.332444332799764</v>
       </c>
       <c r="F9" t="n">
-        <v>2.055134106532548</v>
+        <v>2.035982262816186</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3392209102651103</v>
+        <v>0.3514791575998789</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>10.98185762522007</v>
+        <v>10.88373856776716</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.752249999999999</v>
+        <v>1.736847332799762</v>
       </c>
       <c r="F10" t="n">
-        <v>2.950666465111455</v>
+        <v>2.922406157559534</v>
       </c>
       <c r="G10" t="n">
-        <v>0.637270868029939</v>
+        <v>0.6441857448776414</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>6.812647495651119</v>
+        <v>6.78953237801823</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.496875</v>
+        <v>1.492380665997279</v>
       </c>
       <c r="F11" t="n">
-        <v>2.292774918630261</v>
+        <v>2.27296394287756</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3766465895281557</v>
+        <v>-0.3529592353630822</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>3.517355613421162</v>
+        <v>3.39571859324704</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8208291666666665</v>
+        <v>0.7935931672002364</v>
       </c>
       <c r="F12" t="n">
-        <v>1.134433580581075</v>
+        <v>1.10354844005021</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3578947458371534</v>
+        <v>0.3923816532652408</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>3.179066843658065</v>
+        <v>3.09201671991579</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7209458333333337</v>
+        <v>0.7022431672002373</v>
       </c>
       <c r="F13" t="n">
-        <v>1.030215017403325</v>
+        <v>1.020248090692468</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5807044125928136</v>
+        <v>0.5887782084472752</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>3.45634223130967</v>
+        <v>3.344107717452549</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7326083333333333</v>
+        <v>0.7084223340027199</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9331701501691246</v>
+        <v>0.9185437129970628</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.296029968442963</v>
+        <v>-0.2557206184239853</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>5.306304315652661</v>
+        <v>5.260494760399082</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.166283333333332</v>
+        <v>1.156680666133094</v>
       </c>
       <c r="F15" t="n">
-        <v>1.62616079821974</v>
+        <v>1.605908518351295</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9210593045179001</v>
+        <v>-0.8735073487248861</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>3.394552454981429</v>
+        <v>3.217836526075883</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7858000000000004</v>
+        <v>0.7456556661330968</v>
       </c>
       <c r="F16" t="n">
-        <v>1.396867469181788</v>
+        <v>1.340931519066684</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1549730236471114</v>
+        <v>-0.0643259033740764</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>7.278607030769709</v>
+        <v>7.101871131440811</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2.041904166666667</v>
+        <v>1.998515166133097</v>
       </c>
       <c r="F17" t="n">
-        <v>3.915861975191414</v>
+        <v>3.921224428480592</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6024811240895016</v>
+        <v>0.6013916393244334</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>1.511692566210809</v>
+        <v>1.665063737812107</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5380999999999986</v>
+        <v>0.5932359994664281</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7461606987327399</v>
+        <v>0.7768187070118353</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03716669899403946</v>
+        <v>-0.04357991681151874</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>5.72198017077879</v>
+        <v>5.704092649957776</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5606625</v>
+        <v>1.563109833866904</v>
       </c>
       <c r="F19" t="n">
-        <v>2.739330805522278</v>
+        <v>2.745351478977412</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6897755102693368</v>
+        <v>0.6884103499263488</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>4.70422784901848</v>
+        <v>4.570646782106505</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.527295833333333</v>
+        <v>1.485323500533569</v>
       </c>
       <c r="F20" t="n">
-        <v>1.992790016220976</v>
+        <v>1.96508423541219</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6100778977674131</v>
+        <v>0.62084471055574</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>4.190443868565334</v>
+        <v>4.121463385984865</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.360823611111112</v>
+        <v>1.338737610577542</v>
       </c>
       <c r="F21" t="n">
-        <v>2.312003256467574</v>
+        <v>2.293376736200589</v>
       </c>
       <c r="G21" t="n">
-        <v>0.125208162819319</v>
+        <v>0.1392468028472054</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>3.758926452642829</v>
+        <v>3.774318094279024</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.378229166666666</v>
+        <v>1.383048499330613</v>
       </c>
       <c r="F22" t="n">
-        <v>1.661132796843767</v>
+        <v>1.663917564887547</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.03314552695477091</v>
+        <v>-0.03661241684234273</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>5.193703743434939</v>
+        <v>5.15331943571617</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.732583333333333</v>
+        <v>1.715689000669387</v>
       </c>
       <c r="F23" t="n">
-        <v>2.276139393432074</v>
+        <v>2.246363713684004</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6441270916594571</v>
+        <v>0.6533770073807199</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>2.859052850448966</v>
+        <v>2.846913906521592</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.107550000004851</v>
+        <v>1.103930667200237</v>
       </c>
       <c r="F24" t="n">
-        <v>1.436311932531855</v>
+        <v>1.44144875764901</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2555706201655159</v>
+        <v>0.2502363448852384</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>4.155679699954291</v>
+        <v>4.206508215329138</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.557908333333334</v>
+        <v>1.575235999466431</v>
       </c>
       <c r="F25" t="n">
-        <v>1.936306010810276</v>
+        <v>1.96199205476443</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.04223407840445814</v>
+        <v>-0.07006897074717933</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>4.1060103096646</v>
+        <v>4.062877290558776</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.540824999995151</v>
+        <v>1.525097334002723</v>
       </c>
       <c r="F26" t="n">
-        <v>2.039262178868735</v>
+        <v>2.020516106436358</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4176244840537449</v>
+        <v>-0.3916810367803696</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>3.144570919947257</v>
+        <v>3.308298249885516</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.211579166729726</v>
+        <v>1.274665167200238</v>
       </c>
       <c r="F27" t="n">
-        <v>1.548326491372019</v>
+        <v>1.58894956140504</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1395261081809471</v>
+        <v>-0.2001054662435335</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>3.770145562904156</v>
+        <v>3.833093971709457</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.533966667117775</v>
+        <v>1.558255667336055</v>
       </c>
       <c r="F28" t="n">
-        <v>2.13594763654902</v>
+        <v>2.152953945751749</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2661968684146726</v>
+        <v>0.2544653423684295</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>3.817157328613718</v>
+        <v>3.719146818159089</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.478562499995149</v>
+        <v>1.439918165997278</v>
       </c>
       <c r="F29" t="n">
-        <v>1.991540352226951</v>
+        <v>1.966534417286721</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.04562111206111563</v>
+        <v>-0.0195281601752908</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>6.010554744639497</v>
+        <v>6.048706117827108</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2.286375000033953</v>
+        <v>2.300727667200236</v>
       </c>
       <c r="F30" t="n">
-        <v>2.979142003352116</v>
+        <v>2.983532912462349</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4950715774042633</v>
+        <v>-0.4994819487272788</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>4.911836446598086</v>
+        <v>4.916633857144429</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1.971641666666666</v>
+        <v>1.973952667200235</v>
       </c>
       <c r="F31" t="n">
-        <v>2.555327344490328</v>
+        <v>2.555037193859321</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3059736138023794</v>
+        <v>0.3061312145588431</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>3.905248565562907</v>
+        <v>3.922074323087653</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.659200000000001</v>
+        <v>1.666980667336054</v>
       </c>
       <c r="F32" t="n">
-        <v>2.473220296159105</v>
+        <v>2.494495342515772</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5510335687495689</v>
+        <v>-0.5778328308836902</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>4.92305160127466</v>
+        <v>4.988893291010744</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.975750000000001</v>
+        <v>2.002360999466431</v>
       </c>
       <c r="F33" t="n">
-        <v>2.416181506875398</v>
+        <v>2.451451536969509</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.08406729780260935</v>
+        <v>-0.1159474798366114</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>7.432679374280085</v>
+        <v>7.479568663750692</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.4865625</v>
+        <v>2.501256832799764</v>
       </c>
       <c r="F34" t="n">
-        <v>4.180790509331539</v>
+        <v>4.193951399602813</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6316860992107733</v>
+        <v>0.6293635870466066</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>5.506464765861352</v>
+        <v>5.49972823249634</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.199149999999999</v>
+        <v>2.19583900053357</v>
       </c>
       <c r="F35" t="n">
-        <v>2.808382694126045</v>
+        <v>2.804528737804779</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8261274839614932</v>
+        <v>-0.8211189168870434</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>2.671849226459196</v>
+        <v>2.62927120133777</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.097808333333334</v>
+        <v>1.081219332663945</v>
       </c>
       <c r="F36" t="n">
-        <v>1.285101651297153</v>
+        <v>1.26909570023687</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4705292559912675</v>
+        <v>0.4836362451353003</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.2744925683640412</v>
+        <v>0.3387338779145418</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1126999999999973</v>
+        <v>0.1385026659972777</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1126999999999973</v>
+        <v>0.1632170868243699</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9754927514792912</v>
+        <v>0.9485982426715323</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>5.526487596017698</v>
+        <v>5.5835948650417</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2.202679166666667</v>
+        <v>2.22551816599728</v>
       </c>
       <c r="F38" t="n">
-        <v>3.214237799035722</v>
+        <v>3.24987524000017</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1972502177771136</v>
+        <v>-0.2239461056743195</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>4.333262078548036</v>
+        <v>4.295030597636479</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.718845833333333</v>
+        <v>1.702040167336052</v>
       </c>
       <c r="F39" t="n">
-        <v>2.139678308667761</v>
+        <v>2.140241682855156</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1172826548150261</v>
+        <v>0.1168177572327734</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>3.551253442284056</v>
+        <v>3.521792364395385</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.381954166666667</v>
+        <v>1.369584832799764</v>
       </c>
       <c r="F40" t="n">
-        <v>1.864650924771176</v>
+        <v>1.882312004399298</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2031759463564171</v>
+        <v>-0.2260756944122666</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>5.545566604299404</v>
+        <v>5.568448583996275</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2.195958333333333</v>
+        <v>2.206122333866904</v>
       </c>
       <c r="F41" t="n">
-        <v>2.93312780165361</v>
+        <v>2.944178970477283</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2956403694643917</v>
+        <v>-0.3054219508274272</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>4.831854660208456</v>
+        <v>4.877996235978332</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2.0272875</v>
+        <v>2.047476499330612</v>
       </c>
       <c r="F42" t="n">
-        <v>2.667310147804964</v>
+        <v>2.693948271866456</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2841349787996824</v>
+        <v>0.2697650542997916</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>5.616474292616772</v>
+        <v>5.519061893656985</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2.252854166666665</v>
+        <v>2.213859834002719</v>
       </c>
       <c r="F43" t="n">
-        <v>3.006316802514886</v>
+        <v>2.956842102528411</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.3660353012959865</v>
+        <v>-0.3214438111113183</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>4.454635431536754</v>
+        <v>4.498360667522233</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.740729166666666</v>
+        <v>1.758868165997279</v>
       </c>
       <c r="F44" t="n">
-        <v>2.191985810572231</v>
+        <v>2.230250102923208</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.4026237589375496</v>
+        <v>-0.4520208423539935</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>3.330615641154604</v>
+        <v>3.320063020274348</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.329566666666668</v>
+        <v>1.324814000669388</v>
       </c>
       <c r="F45" t="n">
-        <v>1.606271147201908</v>
+        <v>1.604314989114467</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1388742363793988</v>
+        <v>0.1409703612052616</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>4.07650509154271</v>
+        <v>4.048704910725858</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.607062499999999</v>
+        <v>1.595018166133094</v>
       </c>
       <c r="F46" t="n">
-        <v>2.226263803906296</v>
+        <v>2.223647733529644</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.08453911432590488</v>
+        <v>-0.08199173998756182</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>7.544523314314551</v>
+        <v>7.444387162250485</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2.586754166666668</v>
+        <v>2.55517349946643</v>
       </c>
       <c r="F47" t="n">
-        <v>3.87416762463242</v>
+        <v>3.86709104760395</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6935550263509082</v>
+        <v>0.6946735122292731</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>3.678346324270652</v>
+        <v>3.769942580550294</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.463208333333333</v>
+        <v>1.497902665997278</v>
       </c>
       <c r="F48" t="n">
-        <v>1.814818930132333</v>
+        <v>1.851769337560845</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.3206591684485598</v>
+        <v>-0.3749848927453865</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>5.045566586300291</v>
+        <v>5.038526496859316</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.962570833333335</v>
+        <v>1.959876499466431</v>
       </c>
       <c r="F49" t="n">
-        <v>2.498058846968315</v>
+        <v>2.507803560439366</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.4201908479395042</v>
+        <v>-0.4312925447381828</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>4.228520374548744</v>
+        <v>4.227692957532003</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.764395833333332</v>
+        <v>1.764390165997276</v>
       </c>
       <c r="F50" t="n">
-        <v>2.397845065105332</v>
+        <v>2.41876333893612</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.22820052722176</v>
+        <v>-0.2497231020422921</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>3.971090463221413</v>
+        <v>3.96154262177633</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.571933333333334</v>
+        <v>1.568160999466429</v>
       </c>
       <c r="F51" t="n">
-        <v>2.157166339591518</v>
+        <v>2.138817841040778</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.3331311826950425</v>
+        <v>-0.3105488489044765</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>4.493358040118413</v>
+        <v>4.427556693723625</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.7865</v>
+        <v>1.75969733400272</v>
       </c>
       <c r="F52" t="n">
-        <v>2.311071877758601</v>
+        <v>2.284793907038792</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.7770593526519098</v>
+        <v>-0.7368771084111427</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>2.390395020570546</v>
+        <v>2.432232690917284</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9338124999999996</v>
+        <v>0.9515901661330955</v>
       </c>
       <c r="F53" t="n">
-        <v>1.596132404830501</v>
+        <v>1.601951333181228</v>
       </c>
       <c r="G53" t="n">
-        <v>0.009105584679654943</v>
+        <v>0.001867521128872673</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>3.406983616014978</v>
+        <v>3.436819780933557</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1.342545833333333</v>
+        <v>1.354423500669387</v>
       </c>
       <c r="F54" t="n">
-        <v>1.756785179549091</v>
+        <v>1.752196316414759</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.08672107221913983</v>
+        <v>-0.0810512824860492</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>4.319621136134319</v>
+        <v>4.352273578030679</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.7489375</v>
+        <v>1.760006832799764</v>
       </c>
       <c r="F55" t="n">
-        <v>2.587793534316447</v>
+        <v>2.599185801951905</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.4689948725269739</v>
+        <v>-0.4819572818120617</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>1.815391424715606</v>
+        <v>1.851562422076086</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.739191666666669</v>
+        <v>0.7536610006693879</v>
       </c>
       <c r="F56" t="n">
-        <v>1.163243764579608</v>
+        <v>1.140669571986769</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.03172493204087412</v>
+        <v>0.007930329977074324</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>5.70739775741431</v>
+        <v>5.621825570026518</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2.2749375</v>
+        <v>2.238868167200236</v>
       </c>
       <c r="F57" t="n">
-        <v>3.123148077461266</v>
+        <v>3.090625300036284</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.2301975526356006</v>
+        <v>-0.2047097295486338</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>4.651185284759365</v>
+        <v>4.600342502467809</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.771404166666668</v>
+        <v>1.752301500669389</v>
       </c>
       <c r="F58" t="n">
-        <v>2.401906096598076</v>
+        <v>2.380477880341486</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1359498192337223</v>
+        <v>0.1512980167570483</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>5.213371310095813</v>
+        <v>5.146032479971232</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2.102658333333333</v>
+        <v>2.075155667336053</v>
       </c>
       <c r="F59" t="n">
-        <v>2.91759954343178</v>
+        <v>2.880029509543161</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.2116505565784088</v>
+        <v>-0.1806465348273172</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>4.01544060921674</v>
+        <v>4.061140166371481</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.587583333333334</v>
+        <v>1.60991399946643</v>
       </c>
       <c r="F60" t="n">
-        <v>2.138688666761325</v>
+        <v>2.13041660419078</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6837899644420791</v>
+        <v>0.6862313208621178</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>4.745272356930686</v>
+        <v>4.688111068540437</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.979200000000001</v>
+        <v>1.955847334002722</v>
       </c>
       <c r="F61" t="n">
-        <v>2.494111127235514</v>
+        <v>2.478717710385148</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1486495321278354</v>
+        <v>0.1591260104958501</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>4.219817097123104</v>
+        <v>4.188557163810748</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.620525000000001</v>
+        <v>1.609494334002722</v>
       </c>
       <c r="F62" t="n">
-        <v>2.169003649720304</v>
+        <v>2.134792049494328</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.07640320131216694</v>
+        <v>-0.04271487377586958</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>4.47178989519956</v>
+        <v>4.45792750523508</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.805029166666667</v>
+        <v>1.801365167336054</v>
       </c>
       <c r="F63" t="n">
-        <v>2.796165160611345</v>
+        <v>2.789781308785087</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.3308494157397954</v>
+        <v>-0.3247794974411122</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>5.942118197607523</v>
+        <v>5.9366426640155</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2.3219375</v>
+        <v>2.319934834002722</v>
       </c>
       <c r="F64" t="n">
-        <v>3.45515435068874</v>
+        <v>3.439634704083197</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.2056022249657368</v>
+        <v>-0.1947960512266593</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>6.143586928665279</v>
+        <v>6.129242176660502</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2.367483333333334</v>
+        <v>2.362963999466431</v>
       </c>
       <c r="F65" t="n">
-        <v>3.224898767145</v>
+        <v>3.20814155663052</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1517454385495276</v>
+        <v>-0.139807142961236</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>4.884518812440886</v>
+        <v>4.792193732163969</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.85275</v>
+        <v>1.816788999466429</v>
       </c>
       <c r="F66" t="n">
-        <v>2.669787549444087</v>
+        <v>2.640373602139362</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.4942706902018541</v>
+        <v>-0.4615263018574403</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>3.867272557009777</v>
+        <v>3.819554731410166</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.524679166666667</v>
+        <v>1.506831834002719</v>
       </c>
       <c r="F67" t="n">
-        <v>2.036005618903919</v>
+        <v>2.021095923390238</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.891589395461829</v>
+        <v>-0.8639865675374327</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>2.203448373818924</v>
+        <v>2.11556610124609</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9326958333333337</v>
+        <v>0.8948431673360538</v>
       </c>
       <c r="F68" t="n">
-        <v>1.324933504463525</v>
+        <v>1.282632841203439</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7470006114804325</v>
+        <v>0.7628975630341102</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>6.895205501138914</v>
+        <v>6.904707794944043</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2.81935</v>
+        <v>2.82293600053357</v>
       </c>
       <c r="F69" t="n">
-        <v>3.233294881644214</v>
+        <v>3.239139427181103</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.2901805190045055</v>
+        <v>-0.294849028521839</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>2.904253364111011</v>
+        <v>2.856729800260104</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.153849999999999</v>
+        <v>1.134760999466428</v>
       </c>
       <c r="F70" t="n">
-        <v>1.620380234440874</v>
+        <v>1.580631867019218</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.4607380288564302</v>
+        <v>-0.3899524034444779</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>3.857987592398426</v>
+        <v>3.830733030697596</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.522416666666667</v>
+        <v>1.512014000669388</v>
       </c>
       <c r="F71" t="n">
-        <v>2.146474058970509</v>
+        <v>2.129753624138527</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.5677911037200929</v>
+        <v>-0.543460925199996</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>2.809703442845686</v>
+        <v>2.848731069373272</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1.131495833333333</v>
+        <v>1.147784832799764</v>
       </c>
       <c r="F72" t="n">
-        <v>1.780041765076503</v>
+        <v>1.772299461932348</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.3330932860619964</v>
+        <v>-0.3215219100950431</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>3.522163523956185</v>
+        <v>3.528928516537696</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.407820833333334</v>
+        <v>1.410951499466429</v>
       </c>
       <c r="F73" t="n">
-        <v>1.983451075251584</v>
+        <v>1.991522283258668</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.1034977531389756</v>
+        <v>-0.1124968977444161</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>2.198786342316326</v>
+        <v>2.265956117841338</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9231000000000013</v>
+        <v>0.9505056673360563</v>
       </c>
       <c r="F74" t="n">
-        <v>1.258900704649365</v>
+        <v>1.284980963938725</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5938377820542635</v>
+        <v>0.5768347889260403</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>6.849477168929775</v>
+        <v>6.859171086230309</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2.305429166666667</v>
+        <v>2.309173499330614</v>
       </c>
       <c r="F75" t="n">
-        <v>3.831305815553187</v>
+        <v>3.844223467352401</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5663990304415425</v>
+        <v>0.5634702385490817</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>2.638228024859346</v>
+        <v>2.694519120416044</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1.036454166666666</v>
+        <v>1.058309832663943</v>
       </c>
       <c r="F76" t="n">
-        <v>1.599439669201894</v>
+        <v>1.610373315143729</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.163983574007545</v>
+        <v>-1.193670345483486</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>3.626090782684265</v>
+        <v>3.606994003545943</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.559970833333334</v>
+        <v>1.551826499466429</v>
       </c>
       <c r="F77" t="n">
-        <v>2.096324560490733</v>
+        <v>2.081357148410114</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.7258759529207655</v>
+        <v>-0.7013189932504438</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>1.629350556924891</v>
+        <v>1.63228432830834</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7432333333333325</v>
+        <v>0.7440359993306123</v>
       </c>
       <c r="F78" t="n">
-        <v>1.027625663848466</v>
+        <v>1.042746082632201</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1328965040465264</v>
+        <v>-0.1664805105455118</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>2.116095413294667</v>
+        <v>2.126781834517422</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8679833333333337</v>
+        <v>0.8744973340027213</v>
       </c>
       <c r="F79" t="n">
-        <v>1.363806920901928</v>
+        <v>1.343750225346638</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7799517409828443</v>
+        <v>0.7863763865081028</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>4.074532118398058</v>
+        <v>4.081367870766081</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1.6108375</v>
+        <v>1.613431832663945</v>
       </c>
       <c r="F80" t="n">
-        <v>2.194284881895846</v>
+        <v>2.188917347950659</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5780845973618394</v>
+        <v>-0.5703735997760129</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>4.438214894978524</v>
+        <v>4.399966330128347</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.800583333333333</v>
+        <v>1.784727666133096</v>
       </c>
       <c r="F81" t="n">
-        <v>2.161521636727624</v>
+        <v>2.169461078710395</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.4484276886548026</v>
+        <v>-0.4590876118105927</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>2.527165841438336</v>
+        <v>2.551568671604381</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1.025541666666666</v>
+        <v>1.035913999330611</v>
       </c>
       <c r="F82" t="n">
-        <v>1.347137660003608</v>
+        <v>1.363815743909515</v>
       </c>
       <c r="G82" t="n">
-        <v>-1.454293210060177</v>
+        <v>-1.515439582708118</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>4.70997328997899</v>
+        <v>4.667402309690752</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.967921739130435</v>
+        <v>1.947994087513291</v>
       </c>
       <c r="F83" t="n">
-        <v>2.809087424769831</v>
+        <v>2.807665806140812</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.386091909310831</v>
+        <v>-0.384689321801353</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
